--- a/Result/profitability/4549.xlsx
+++ b/Result/profitability/4549.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM54"/>
+  <dimension ref="A1:AM55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7288,6 +7288,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>4549</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>307</v>
+      </c>
+      <c r="D55" t="n">
+        <v>114</v>
+      </c>
+      <c r="E55" t="n">
+        <v>194</v>
+      </c>
+      <c r="F55" t="n">
+        <v>62.97</v>
+      </c>
+      <c r="G55" t="n">
+        <v>85</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>27.75%</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>20</v>
+      </c>
+      <c r="J55" t="n">
+        <v>105</v>
+      </c>
+      <c r="K55" t="n">
+        <v>87</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="N55" t="n">
+        <v>56.335</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
+      </c>
+      <c r="V55" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1.067567567567568</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0.5899999999999963</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0.009458159666559718</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.942307692307692</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.2511424597655474</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK55" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
